--- a/design/tables/ArtCut.xlsx
+++ b/design/tables/ArtCut.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtCut" sheetId="1" r:id="Rdb1a19c1a6174c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtCut" sheetId="1" r:id="R004f6ab94c994b27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -505,19 +505,17 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E6" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_87.png</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="str">
-        <x:v>64:38</x:v>
-      </x:c>
+        <x:v>769e58de6e98c54be1191d7737aca208b8599b03e3b099e7fae0d3afdec7f958</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="str"/>
       <x:c r="H6" s="1" t="n">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I6" s="1" t="n">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J6" s="1" t="n">
         <x:v>306</x:v>
@@ -529,7 +527,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M6" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N6" s="1" t="n">
         <x:v>8</x:v>
@@ -549,19 +547,17 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_88.png</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="str">
-        <x:v>427:130</x:v>
-      </x:c>
+        <x:v>c7e62aebc57bc99374a2579d5933f742ee98ad34f54b74c4c85fce485c0f773e</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="str"/>
       <x:c r="H7" s="1" t="n">
-        <x:v>376</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="1" t="n">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J7" s="1" t="n">
         <x:v>334</x:v>
@@ -573,7 +569,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M7" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N7" s="1" t="n">
         <x:v>8</x:v>
@@ -593,19 +589,17 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="E8" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_89.png</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="str">
-        <x:v>800:129</x:v>
-      </x:c>
+        <x:v>9bd142b67de021ad28e9e191976b6bac9ac03686efaf65693e309ad82260840f</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="str"/>
       <x:c r="H8" s="1" t="n">
-        <x:v>745</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I8" s="1" t="n">
-        <x:v>127</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J8" s="1" t="n">
         <x:v>319</x:v>
@@ -617,7 +611,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M8" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N8" s="1" t="n">
         <x:v>8</x:v>
@@ -637,31 +631,29 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_90.png</x:v>
       </x:c>
       <x:c r="F9" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="str">
-        <x:v>165:406</x:v>
-      </x:c>
+        <x:v>3763450642cf5efb95445962925d2425e69d4333ef142e6ce54ea27f9beb66d4</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="str"/>
       <x:c r="H9" s="1" t="n">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I9" s="1" t="n">
-        <x:v>404</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J9" s="1" t="n">
-        <x:v>301</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K9" s="1" t="n">
-        <x:v>298</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L9" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M9" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="1" t="n">
         <x:v>8</x:v>
@@ -681,19 +673,17 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_91.png</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="str">
-        <x:v>410:505</x:v>
-      </x:c>
+        <x:v>314f154a5e9e1780c2c65a180bb4c327cef633ade1edbd69d447392619baaa72</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="str"/>
       <x:c r="H10" s="1" t="n">
-        <x:v>377</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I10" s="1" t="n">
-        <x:v>503</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J10" s="1" t="n">
         <x:v>333</x:v>
@@ -705,7 +695,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M10" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="1" t="n">
         <x:v>8</x:v>
@@ -725,19 +715,17 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_92.png</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="str">
-        <x:v>781:509</x:v>
-      </x:c>
+        <x:v>97d6517b9d28614d47addbffb82b681eb43e18f6b371caa427cd1d86837f0341</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="str"/>
       <x:c r="H11" s="1" t="n">
-        <x:v>746</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I11" s="1" t="n">
-        <x:v>507</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J11" s="1" t="n">
         <x:v>318</x:v>
@@ -749,7 +737,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M11" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N11" s="1" t="n">
         <x:v>8</x:v>
@@ -769,31 +757,29 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E12" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_93.png</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="str">
-        <x:v>169:824</x:v>
-      </x:c>
+        <x:v>4f0f35df17c27691ad6981252ae164c7196d856b462b10bab0201f5d6ed295ed</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="str"/>
       <x:c r="H12" s="1" t="n">
-        <x:v>89</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I12" s="1" t="n">
-        <x:v>822</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J12" s="1" t="n">
-        <x:v>183</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K12" s="1" t="n">
-        <x:v>183</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M12" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="1" t="n">
         <x:v>8</x:v>
@@ -813,19 +799,17 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="E13" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_94.png</x:v>
       </x:c>
       <x:c r="F13" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="str">
-        <x:v>419:884</x:v>
-      </x:c>
+        <x:v>3abf10025205cf2b6ad4bff35cae9248fe0b81fe77b7079dec3b3f53bedc438f</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="str"/>
       <x:c r="H13" s="1" t="n">
-        <x:v>373</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I13" s="1" t="n">
-        <x:v>882</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J13" s="1" t="n">
         <x:v>341</x:v>
@@ -837,7 +821,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M13" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="1" t="n">
         <x:v>8</x:v>
@@ -857,19 +841,17 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_95.png</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="str">
-        <x:v>775:865</x:v>
-      </x:c>
+        <x:v>df407cc9d8a3c7982e30f99332d7832043c41adffc9450251299fec2062a8181</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="str"/>
       <x:c r="H14" s="1" t="n">
-        <x:v>754</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I14" s="1" t="n">
-        <x:v>863</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J14" s="1" t="n">
         <x:v>302</x:v>
@@ -881,7 +863,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M14" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="1" t="n">
         <x:v>8</x:v>
@@ -901,19 +883,17 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_96.png</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="str">
-        <x:v>416:1171</x:v>
-      </x:c>
+        <x:v>11f9467e4fc48aeba66392eac83bfc1564c3952bfd70783143e0dec6a722e7c3</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="str"/>
       <x:c r="H15" s="1" t="n">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I15" s="1" t="n">
-        <x:v>1169</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J15" s="1" t="n">
         <x:v>490</x:v>
@@ -925,7 +905,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M15" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="1" t="n">
         <x:v>8</x:v>
@@ -945,19 +925,17 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E16" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_97.png</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="str">
-        <x:v>573:1127</x:v>
-      </x:c>
+        <x:v>039daea8699cafaba35a1724f03e756d8d32061941b4f99fd5d0d0a81befb8fc</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="str"/>
       <x:c r="H16" s="1" t="n">
-        <x:v>532</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I16" s="1" t="n">
-        <x:v>1125</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J16" s="1" t="n">
         <x:v>227</x:v>
@@ -969,7 +947,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M16" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="1" t="n">
         <x:v>8</x:v>
@@ -989,19 +967,17 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="E17" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/skin_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_98.png</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>582dc911de7fadfe7a589c1710d8299f547fc85b0d3d1a069d67d82526619d53</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="str">
-        <x:v>827:1190</x:v>
-      </x:c>
+        <x:v>e466d4e09de60b0f72a1f2c7f7b23357d5a99739ff042ab66fdc934f71e17062</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="str"/>
       <x:c r="H17" s="1" t="n">
-        <x:v>778</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I17" s="1" t="n">
-        <x:v>1188</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J17" s="1" t="n">
         <x:v>282</x:v>
@@ -1013,7 +989,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M17" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="1" t="n">
         <x:v>8</x:v>
@@ -1033,31 +1009,29 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E18" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_100.png</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="str">
-        <x:v>100:147</x:v>
-      </x:c>
+        <x:v>1690197823b1fe29fd5046efe91c4291bc3d9c77ec6aa66f481a6516fb4a2f07</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="str"/>
       <x:c r="H18" s="1" t="n">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I18" s="1" t="n">
-        <x:v>145</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J18" s="1" t="n">
-        <x:v>274</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K18" s="1" t="n">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L18" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M18" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N18" s="1" t="n">
         <x:v>8</x:v>
@@ -1077,31 +1051,29 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="E19" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_101.png</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="str">
-        <x:v>494:147</x:v>
-      </x:c>
+        <x:v>702ac5a79138c402626fa50d42246a3616840e1251ed2828eddd74221ea6a84d</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="str"/>
       <x:c r="H19" s="1" t="n">
-        <x:v>322</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I19" s="1" t="n">
-        <x:v>145</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J19" s="1" t="n">
-        <x:v>294</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K19" s="1" t="n">
-        <x:v>250</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L19" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M19" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N19" s="1" t="n">
         <x:v>8</x:v>
@@ -1121,31 +1093,29 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_28.png</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="str">
-        <x:v>494:147</x:v>
-      </x:c>
+        <x:v>702ac5a79138c402626fa50d42246a3616840e1251ed2828eddd74221ea6a84d</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="str"/>
       <x:c r="H20" s="1" t="n">
-        <x:v>322</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I20" s="1" t="n">
-        <x:v>145</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J20" s="1" t="n">
-        <x:v>294</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K20" s="1" t="n">
-        <x:v>250</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L20" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M20" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N20" s="1" t="n">
         <x:v>8</x:v>
@@ -1165,31 +1135,29 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="E21" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_102.png</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="str">
-        <x:v>727:159</x:v>
-      </x:c>
+        <x:v>f85037d6a30555cb78519e4b28156380e79db7a0633909af7947dd74686653f4</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="str"/>
       <x:c r="H21" s="1" t="n">
-        <x:v>634</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I21" s="1" t="n">
-        <x:v>157</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J21" s="1" t="n">
-        <x:v>323</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K21" s="1" t="n">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L21" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M21" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N21" s="1" t="n">
         <x:v>8</x:v>
@@ -1209,31 +1177,29 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E22" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_103.png</x:v>
       </x:c>
       <x:c r="F22" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="str">
-        <x:v>1040:137</x:v>
-      </x:c>
+        <x:v>d88f46d6e61484f19932c0191cf3aff646232b0932bb72c0351bcebf47bc8ca6</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="str"/>
       <x:c r="H22" s="1" t="n">
-        <x:v>970</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I22" s="1" t="n">
-        <x:v>135</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J22" s="1" t="n">
-        <x:v>259</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K22" s="1" t="n">
-        <x:v>266</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L22" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M22" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N22" s="1" t="n">
         <x:v>8</x:v>
@@ -1253,31 +1219,29 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="E23" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_104.png</x:v>
       </x:c>
       <x:c r="F23" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="str">
-        <x:v>116:504</x:v>
-      </x:c>
+        <x:v>6637769062462a0729b7fd1e110a7176fa8e5a68ad564ddc50811936669adb6b</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="str"/>
       <x:c r="H23" s="1" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:v>502</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
-        <x:v>295</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K23" s="1" t="n">
-        <x:v>277</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L23" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M23" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N23" s="1" t="n">
         <x:v>8</x:v>
@@ -1297,31 +1261,29 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="E24" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_105.png</x:v>
       </x:c>
       <x:c r="F24" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="str">
-        <x:v>406:499</x:v>
-      </x:c>
+        <x:v>f3a5b73af6058bc5a579ccd59b8896eb29684e98ead3fef4c204e76644d3fb30</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="str"/>
       <x:c r="H24" s="1" t="n">
-        <x:v>342</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:v>497</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
-        <x:v>271</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K24" s="1" t="n">
-        <x:v>272</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M24" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N24" s="1" t="n">
         <x:v>8</x:v>
@@ -1341,31 +1303,29 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="E25" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_106.png</x:v>
       </x:c>
       <x:c r="F25" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="str">
-        <x:v>768:505</x:v>
-      </x:c>
+        <x:v>863bca2940a5b686475197543d2d8a0bc36a67f104e150b8d69cd17835de5a69</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="str"/>
       <x:c r="H25" s="1" t="n">
-        <x:v>625</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:v>503</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
-        <x:v>341</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K25" s="1" t="n">
-        <x:v>287</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M25" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N25" s="1" t="n">
         <x:v>8</x:v>
@@ -1385,31 +1345,29 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E26" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_107.png</x:v>
       </x:c>
       <x:c r="F26" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="str">
-        <x:v>1101:516</x:v>
-      </x:c>
+        <x:v>214d48e7e7538e589f991f5fbc3ea884828052faa94023962d43e9ceb2d80905</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="str"/>
       <x:c r="H26" s="1" t="n">
-        <x:v>984</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:v>514</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
-        <x:v>252</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K26" s="1" t="n">
-        <x:v>252</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M26" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N26" s="1" t="n">
         <x:v>8</x:v>
@@ -1429,31 +1387,29 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E27" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_108.png</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="str">
-        <x:v>186:872</x:v>
-      </x:c>
+        <x:v>18c15afbe0ae8a77eabba7ebfd91cd3ca3688767d465af42a48ff6cea2351cb2</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="str"/>
       <x:c r="H27" s="1" t="n">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:v>870</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
-        <x:v>209</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K27" s="1" t="n">
-        <x:v>299</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M27" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N27" s="1" t="n">
         <x:v>8</x:v>
@@ -1473,31 +1429,29 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E28" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_26.png</x:v>
       </x:c>
       <x:c r="F28" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="str">
-        <x:v>186:872</x:v>
-      </x:c>
+        <x:v>18c15afbe0ae8a77eabba7ebfd91cd3ca3688767d465af42a48ff6cea2351cb2</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="str"/>
       <x:c r="H28" s="1" t="n">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:v>870</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
-        <x:v>209</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K28" s="1" t="n">
-        <x:v>299</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M28" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N28" s="1" t="n">
         <x:v>8</x:v>
@@ -1517,31 +1471,29 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="E29" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_109.png</x:v>
       </x:c>
       <x:c r="F29" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="str">
-        <x:v>520:872</x:v>
-      </x:c>
+        <x:v>26360de7da9a5c22821a30c24df39038754ab40363635953a260d1d7a66bf540</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="str"/>
       <x:c r="H29" s="1" t="n">
-        <x:v>332</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I29" s="1" t="n">
-        <x:v>870</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J29" s="1" t="n">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K29" s="1" t="n">
-        <x:v>295</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L29" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M29" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N29" s="1" t="n">
         <x:v>8</x:v>
@@ -1561,31 +1513,29 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E30" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_27.png</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="str">
-        <x:v>520:872</x:v>
-      </x:c>
+        <x:v>26360de7da9a5c22821a30c24df39038754ab40363635953a260d1d7a66bf540</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="str"/>
       <x:c r="H30" s="1" t="n">
-        <x:v>332</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:v>870</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K30" s="1" t="n">
-        <x:v>295</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L30" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M30" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N30" s="1" t="n">
         <x:v>8</x:v>
@@ -1605,31 +1555,29 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="E31" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_110.png</x:v>
       </x:c>
       <x:c r="F31" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="str">
-        <x:v>764:890</x:v>
-      </x:c>
+        <x:v>ec6c9f6e237ece2b25615c8583c0821083d9974a844802ab5fc6a37b3ea87252</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="str"/>
       <x:c r="H31" s="1" t="n">
-        <x:v>635</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I31" s="1" t="n">
-        <x:v>888</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J31" s="1" t="n">
-        <x:v>277</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K31" s="1" t="n">
-        <x:v>276</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L31" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M31" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N31" s="1" t="n">
         <x:v>8</x:v>
@@ -1649,31 +1597,29 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="E32" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/icon_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_111.png</x:v>
       </x:c>
       <x:c r="F32" s="1" t="str">
-        <x:v>2f1faedf9b0c2cf4dd1ce6cca42be79c8ad64b345de442f75dc8eb10ab92b8c8</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="str">
-        <x:v>1078:890</x:v>
-      </x:c>
+        <x:v>eed35b6e2e5ce45d07560c0c39586128aff7ed66f381b13d4bd5ae8420fe8496</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="str"/>
       <x:c r="H32" s="1" t="n">
-        <x:v>952</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I32" s="1" t="n">
-        <x:v>888</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J32" s="1" t="n">
-        <x:v>276</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K32" s="1" t="n">
-        <x:v>276</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L32" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M32" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N32" s="1" t="n">
         <x:v>8</x:v>
@@ -1693,31 +1639,29 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="E33" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_112.png</x:v>
       </x:c>
       <x:c r="F33" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="str">
-        <x:v>227:64</x:v>
-      </x:c>
+        <x:v>d8c6cb88e2b6532f0d5e0ae051f8d5776e1bd8626b64eed43a04d36e31c817aa</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="str"/>
       <x:c r="H33" s="1" t="n">
-        <x:v>94</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I33" s="1" t="n">
-        <x:v>62</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J33" s="1" t="n">
-        <x:v>258</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K33" s="1" t="n">
-        <x:v>355</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L33" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M33" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N33" s="1" t="n">
         <x:v>8</x:v>
@@ -1737,31 +1681,29 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_113.png</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G34" s="1" t="str">
-        <x:v>617:64</x:v>
-      </x:c>
+        <x:v>2f2e593580eb6a14159ff098edf0e4d1bdf8a5a56378ba2ea7f82a36056368bb</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="str"/>
       <x:c r="H34" s="1" t="n">
-        <x:v>425</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I34" s="1" t="n">
-        <x:v>62</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J34" s="1" t="n">
-        <x:v>381</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K34" s="1" t="n">
-        <x:v>358</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L34" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M34" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N34" s="1" t="n">
         <x:v>8</x:v>
@@ -1781,31 +1723,29 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_114.png</x:v>
       </x:c>
       <x:c r="F35" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="str">
-        <x:v>1012:82</x:v>
-      </x:c>
+        <x:v>8a96803b040c711c7b5d3edbe3373f1be654c6c68ba8ba6e94b6e3886e1eda04</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="str"/>
       <x:c r="H35" s="1" t="n">
-        <x:v>853</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I35" s="1" t="n">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J35" s="1" t="n">
-        <x:v>348</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K35" s="1" t="n">
-        <x:v>334</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L35" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M35" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N35" s="1" t="n">
         <x:v>8</x:v>
@@ -1825,31 +1765,29 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="E36" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_115.png</x:v>
       </x:c>
       <x:c r="F36" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="str">
-        <x:v>190:481</x:v>
-      </x:c>
+        <x:v>e4b0dbe92e7c5400599c6a430e1f2dfd96cf5d170d1cef99727b7c0b67e27334</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="str"/>
       <x:c r="H36" s="1" t="n">
-        <x:v>76</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I36" s="1" t="n">
-        <x:v>479</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J36" s="1" t="n">
-        <x:v>296</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K36" s="1" t="n">
-        <x:v>335</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L36" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M36" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N36" s="1" t="n">
         <x:v>8</x:v>
@@ -1869,31 +1807,29 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_116.png</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="str">
-        <x:v>649:467</x:v>
-      </x:c>
+        <x:v>900dd0effa5cd4e5469dd4aba055dfbfb8ba0ea868b27ba08c93836431320f4e</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="str"/>
       <x:c r="H37" s="1" t="n">
-        <x:v>443</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I37" s="1" t="n">
-        <x:v>465</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J37" s="1" t="n">
-        <x:v>346</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K37" s="1" t="n">
-        <x:v>347</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L37" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M37" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N37" s="1" t="n">
         <x:v>8</x:v>
@@ -1913,31 +1849,29 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="E38" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_117.png</x:v>
       </x:c>
       <x:c r="F38" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="str">
-        <x:v>931:514</x:v>
-      </x:c>
+        <x:v>87666d52b51c81969d388ce8d7658194b17a2b73f92c9a75874d8c00492e1b60</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="str"/>
       <x:c r="H38" s="1" t="n">
-        <x:v>841</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I38" s="1" t="n">
-        <x:v>512</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J38" s="1" t="n">
-        <x:v>379</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K38" s="1" t="n">
-        <x:v>305</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L38" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M38" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N38" s="1" t="n">
         <x:v>8</x:v>
@@ -1957,31 +1891,29 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="E39" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_118.png</x:v>
       </x:c>
       <x:c r="F39" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="str">
-        <x:v>321:925</x:v>
-      </x:c>
+        <x:v>4c046c3f66d965ea1d187cd13f2d07575f9751d3de33ab1ea2f3ad546594413d</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="str"/>
       <x:c r="H39" s="1" t="n">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I39" s="1" t="n">
-        <x:v>923</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J39" s="1" t="n">
-        <x:v>422</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K39" s="1" t="n">
-        <x:v>253</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L39" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M39" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N39" s="1" t="n">
         <x:v>8</x:v>
@@ -2001,31 +1933,29 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E40" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_119.png</x:v>
       </x:c>
       <x:c r="F40" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="str">
-        <x:v>617:837</x:v>
-      </x:c>
+        <x:v>54a698b2762bb26e702988090ae443ccf60776d5f4c9619092c99ae8d8277f47</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="str"/>
       <x:c r="H40" s="1" t="n">
-        <x:v>527</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I40" s="1" t="n">
-        <x:v>835</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J40" s="1" t="n">
-        <x:v>185</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K40" s="1" t="n">
-        <x:v>365</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L40" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M40" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N40" s="1" t="n">
         <x:v>8</x:v>
@@ -2045,31 +1975,29 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="E41" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/goods_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_120.png</x:v>
       </x:c>
       <x:c r="F41" s="1" t="str">
-        <x:v>564d85df83f313a4a13b2f0315979ac0160e8c444c954e082cf6d7a0d9c82204</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="str">
-        <x:v>1054:871</x:v>
-      </x:c>
+        <x:v>cff3cd3a99960b7e750ff6be0f72b23275bb5b76b6627a53f41d6ebc9c8999ed</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="str"/>
       <x:c r="H41" s="1" t="n">
-        <x:v>841</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I41" s="1" t="n">
-        <x:v>869</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J41" s="1" t="n">
-        <x:v>370</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K41" s="1" t="n">
-        <x:v>321</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L41" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M41" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N41" s="1" t="n">
         <x:v>8</x:v>
@@ -2089,31 +2017,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_1.png</x:v>
       </x:c>
       <x:c r="F42" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="str">
-        <x:v>214:148</x:v>
-      </x:c>
+        <x:v>6fb4a6c6a112889fae53bb08bd3d35ed47a482c49323c41967e9a75b3498f3bc</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="str"/>
       <x:c r="H42" s="1" t="n">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I42" s="1" t="n">
-        <x:v>146</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J42" s="1" t="n">
-        <x:v>346</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K42" s="1" t="n">
-        <x:v>360</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L42" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M42" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N42" s="1" t="n">
         <x:v>8</x:v>
@@ -2133,31 +2059,29 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E43" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_2.png</x:v>
       </x:c>
       <x:c r="F43" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="str">
-        <x:v>577:160</x:v>
-      </x:c>
+        <x:v>996c5cae9d3cb09bcbc56536798f98ad958d56d75c388d3bb1913e707d617411</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="str"/>
       <x:c r="H43" s="1" t="n">
-        <x:v>393</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I43" s="1" t="n">
-        <x:v>158</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J43" s="1" t="n">
-        <x:v>370</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K43" s="1" t="n">
-        <x:v>348</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L43" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M43" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N43" s="1" t="n">
         <x:v>8</x:v>
@@ -2177,31 +2101,29 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E44" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_3.png</x:v>
       </x:c>
       <x:c r="F44" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="str">
-        <x:v>970:157</x:v>
-      </x:c>
+        <x:v>a884781d7302315aa72e2071ae9bae001b6d2dfe636d0f2d2cccc94b38430742</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="str"/>
       <x:c r="H44" s="1" t="n">
-        <x:v>777</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I44" s="1" t="n">
-        <x:v>155</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J44" s="1" t="n">
-        <x:v>376</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K44" s="1" t="n">
-        <x:v>355</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L44" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M44" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N44" s="1" t="n">
         <x:v>8</x:v>
@@ -2221,31 +2143,29 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E45" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_14.png</x:v>
       </x:c>
       <x:c r="F45" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="str">
-        <x:v>1343:176</x:v>
-      </x:c>
+        <x:v>7b0b64bb3644a95b7d2c98b4da81e531e294a76df38964492d6cef92dd58958f</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="str"/>
       <x:c r="H45" s="1" t="n">
-        <x:v>1165</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I45" s="1" t="n">
-        <x:v>174</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J45" s="1" t="n">
-        <x:v>364</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K45" s="1" t="n">
-        <x:v>341</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L45" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M45" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N45" s="1" t="n">
         <x:v>8</x:v>
@@ -2265,31 +2185,29 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_15.png</x:v>
       </x:c>
       <x:c r="F46" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="str">
-        <x:v>249:623</x:v>
-      </x:c>
+        <x:v>5f9a7f190fc52fa5fbd1e644bb4ee3c44333cdb62ad8d255027e7b5ec9fb2f6c</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="str"/>
       <x:c r="H46" s="1" t="n">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I46" s="1" t="n">
-        <x:v>621</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J46" s="1" t="n">
-        <x:v>379</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K46" s="1" t="n">
-        <x:v>323</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L46" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M46" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N46" s="1" t="n">
         <x:v>8</x:v>
@@ -2309,31 +2227,29 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E47" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_16.png</x:v>
       </x:c>
       <x:c r="F47" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="str">
-        <x:v>601:597</x:v>
-      </x:c>
+        <x:v>7d90b700fc4c7212742715458e58bd4a69ca169d6e5a6e604e44c9c80d1f787a</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="str"/>
       <x:c r="H47" s="1" t="n">
-        <x:v>401</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I47" s="1" t="n">
-        <x:v>595</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J47" s="1" t="n">
-        <x:v>372</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K47" s="1" t="n">
-        <x:v>350</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L47" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M47" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N47" s="1" t="n">
         <x:v>8</x:v>
@@ -2353,31 +2269,29 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_17.png</x:v>
       </x:c>
       <x:c r="F48" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="str">
-        <x:v>963:609</x:v>
-      </x:c>
+        <x:v>ed9743b4d02b59830d431c8ad44d0ef7dee2b238b2991705a21dd95fc130d25f</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="str"/>
       <x:c r="H48" s="1" t="n">
-        <x:v>777</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I48" s="1" t="n">
-        <x:v>607</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J48" s="1" t="n">
-        <x:v>376</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K48" s="1" t="n">
-        <x:v>338</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L48" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M48" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N48" s="1" t="n">
         <x:v>8</x:v>
@@ -2397,31 +2311,29 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E49" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/staff_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_18.png</x:v>
       </x:c>
       <x:c r="F49" s="1" t="str">
-        <x:v>8e8cb3088431342f5e09dbb87d661a8317f4beeac068e3fa293d70f8f3a9d4a7</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="str">
-        <x:v>1324:621</x:v>
-      </x:c>
+        <x:v>88858d6e4322e0de76b83002e932afc71e0b1b9dcaad06b8cf465fa854e14409</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="str"/>
       <x:c r="H49" s="1" t="n">
-        <x:v>1168</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I49" s="1" t="n">
-        <x:v>619</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J49" s="1" t="n">
-        <x:v>354</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K49" s="1" t="n">
-        <x:v>320</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L49" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M49" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N49" s="1" t="n">
         <x:v>8</x:v>
@@ -2441,31 +2353,29 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E50" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_8.png</x:v>
       </x:c>
       <x:c r="F50" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="str">
-        <x:v>169:62</x:v>
-      </x:c>
+        <x:v>6cfe0f29a138c22f4455800ee92ef4d046345b2ed59ce5327135472ee4b9ffc3</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="str"/>
       <x:c r="H50" s="1" t="n">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I50" s="1" t="n">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J50" s="1" t="n">
-        <x:v>437</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K50" s="1" t="n">
-        <x:v>421</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L50" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M50" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N50" s="1" t="n">
         <x:v>8</x:v>
@@ -2485,31 +2395,29 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E51" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_11.png</x:v>
       </x:c>
       <x:c r="F51" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="str">
-        <x:v>169:62</x:v>
-      </x:c>
+        <x:v>6cfe0f29a138c22f4455800ee92ef4d046345b2ed59ce5327135472ee4b9ffc3</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="str"/>
       <x:c r="H51" s="1" t="n">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I51" s="1" t="n">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J51" s="1" t="n">
-        <x:v>437</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K51" s="1" t="n">
-        <x:v>421</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L51" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M51" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N51" s="1" t="n">
         <x:v>8</x:v>
@@ -2529,31 +2437,29 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E52" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_9.png</x:v>
       </x:c>
       <x:c r="F52" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="str">
-        <x:v>770:42</x:v>
-      </x:c>
+        <x:v>ca6a66f7ff853ebc348a0d258b020b14ce532bbf37d6218ad25b8b262bf0a59c</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="str"/>
       <x:c r="H52" s="1" t="n">
-        <x:v>541</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I52" s="1" t="n">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J52" s="1" t="n">
-        <x:v>449</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K52" s="1" t="n">
-        <x:v>444</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L52" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M52" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N52" s="1" t="n">
         <x:v>8</x:v>
@@ -2573,31 +2479,29 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E53" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_12.png</x:v>
       </x:c>
       <x:c r="F53" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="str">
-        <x:v>770:42</x:v>
-      </x:c>
+        <x:v>ca6a66f7ff853ebc348a0d258b020b14ce532bbf37d6218ad25b8b262bf0a59c</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="str"/>
       <x:c r="H53" s="1" t="n">
-        <x:v>541</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I53" s="1" t="n">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J53" s="1" t="n">
-        <x:v>449</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K53" s="1" t="n">
-        <x:v>444</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L53" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M53" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N53" s="1" t="n">
         <x:v>8</x:v>
@@ -2617,31 +2521,29 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E54" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_19.png</x:v>
       </x:c>
       <x:c r="F54" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="str">
-        <x:v>1269:44</x:v>
-      </x:c>
+        <x:v>1cb42ba7f4eb6a0f698f9cca9efd3c33fc001fde6074f1350eac90e4e8d07d86</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="str"/>
       <x:c r="H54" s="1" t="n">
-        <x:v>1051</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I54" s="1" t="n">
-        <x:v>42</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J54" s="1" t="n">
-        <x:v>448</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K54" s="1" t="n">
-        <x:v>444</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L54" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M54" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N54" s="1" t="n">
         <x:v>8</x:v>
@@ -2661,31 +2563,29 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E55" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_20.png</x:v>
       </x:c>
       <x:c r="F55" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G55" s="1" t="str">
-        <x:v>283:548</x:v>
-      </x:c>
+        <x:v>21cc0fb01c52c400cce73e890e145410cb50b821bf845a44859f660563b044cb</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="str"/>
       <x:c r="H55" s="1" t="n">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I55" s="1" t="n">
-        <x:v>546</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J55" s="1" t="n">
-        <x:v>444</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K55" s="1" t="n">
-        <x:v>416</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L55" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M55" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N55" s="1" t="n">
         <x:v>8</x:v>
@@ -2705,31 +2605,29 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E56" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_21.png</x:v>
       </x:c>
       <x:c r="F56" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G56" s="1" t="str">
-        <x:v>808:552</x:v>
-      </x:c>
+        <x:v>9c66bb7b53a066f4858c11abff5534d0fb55af2dad5757fb180c7de305bb42f8</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="str"/>
       <x:c r="H56" s="1" t="n">
-        <x:v>533</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I56" s="1" t="n">
-        <x:v>550</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J56" s="1" t="n">
-        <x:v>448</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K56" s="1" t="n">
-        <x:v>409</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L56" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M56" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N56" s="1" t="n">
         <x:v>8</x:v>
@@ -2749,31 +2647,29 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E57" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_10.png</x:v>
       </x:c>
       <x:c r="F57" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G57" s="1" t="str">
-        <x:v>1200:576</x:v>
-      </x:c>
+        <x:v>810ef31495fa3bc2233f4738f388ddbf64879c4f41e4cb3b8c4517f161ed1ad1</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="str"/>
       <x:c r="H57" s="1" t="n">
-        <x:v>1029</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I57" s="1" t="n">
-        <x:v>574</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J57" s="1" t="n">
-        <x:v>474</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K57" s="1" t="n">
-        <x:v>381</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L57" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M57" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N57" s="1" t="n">
         <x:v>8</x:v>
@@ -2793,31 +2689,29 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E58" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/enemy_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_13.png</x:v>
       </x:c>
       <x:c r="F58" s="1" t="str">
-        <x:v>2a802edc30fd5c2e6594474035e36a5f63353f6cb5c6e63628aa3d64067e96ad</x:v>
-      </x:c>
-      <x:c r="G58" s="1" t="str">
-        <x:v>1200:576</x:v>
-      </x:c>
+        <x:v>810ef31495fa3bc2233f4738f388ddbf64879c4f41e4cb3b8c4517f161ed1ad1</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="str"/>
       <x:c r="H58" s="1" t="n">
-        <x:v>1029</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I58" s="1" t="n">
-        <x:v>574</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J58" s="1" t="n">
-        <x:v>474</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K58" s="1" t="n">
-        <x:v>381</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L58" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M58" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N58" s="1" t="n">
         <x:v>8</x:v>
@@ -2837,31 +2731,29 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E59" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_5.png</x:v>
       </x:c>
       <x:c r="F59" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G59" s="1" t="str">
-        <x:v>141:155</x:v>
-      </x:c>
+        <x:v>1a1173fc264c86f6a7c4f98930d2ea93ac9be9506858b513c244088f58bd0a58</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="str"/>
       <x:c r="H59" s="1" t="n">
-        <x:v>44</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I59" s="1" t="n">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J59" s="1" t="n">
-        <x:v>309</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K59" s="1" t="n">
-        <x:v>313</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L59" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M59" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N59" s="1" t="n">
         <x:v>8</x:v>
@@ -2881,31 +2773,29 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E60" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_6.png</x:v>
       </x:c>
       <x:c r="F60" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G60" s="1" t="str">
-        <x:v>560:151</x:v>
-      </x:c>
+        <x:v>78d802305b416fda4e1c3319f4ae99599435da0361383d60ee22e7490422be42</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="str"/>
       <x:c r="H60" s="1" t="n">
-        <x:v>427</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I60" s="1" t="n">
-        <x:v>149</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J60" s="1" t="n">
-        <x:v>328</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K60" s="1" t="n">
-        <x:v>310</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L60" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M60" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N60" s="1" t="n">
         <x:v>8</x:v>
@@ -2925,31 +2815,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E61" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_7.png</x:v>
       </x:c>
       <x:c r="F61" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G61" s="1" t="str">
-        <x:v>955:144</x:v>
-      </x:c>
+        <x:v>49e22347abe1c520fa818c8d9cddc0afb52bd3a0298b8b54616f68c6eeebddf5</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="str"/>
       <x:c r="H61" s="1" t="n">
-        <x:v>825</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I61" s="1" t="n">
-        <x:v>142</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J61" s="1" t="n">
-        <x:v>263</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K61" s="1" t="n">
-        <x:v>317</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L61" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M61" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N61" s="1" t="n">
         <x:v>8</x:v>
@@ -2969,31 +2857,29 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E62" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_32.png</x:v>
       </x:c>
       <x:c r="F62" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G62" s="1" t="str">
-        <x:v>1332:71</x:v>
-      </x:c>
+        <x:v>7c47a66483b8d48fd0b6b84a66d2991e4bd28ad83e15e46f14b6d5f7d3aee4b0</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="str"/>
       <x:c r="H62" s="1" t="n">
-        <x:v>1169</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I62" s="1" t="n">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J62" s="1" t="n">
-        <x:v>322</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K62" s="1" t="n">
-        <x:v>413</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L62" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M62" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N62" s="1" t="n">
         <x:v>8</x:v>
@@ -3013,31 +2899,29 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E63" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_35.png</x:v>
       </x:c>
       <x:c r="F63" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G63" s="1" t="str">
-        <x:v>1332:71</x:v>
-      </x:c>
+        <x:v>7c47a66483b8d48fd0b6b84a66d2991e4bd28ad83e15e46f14b6d5f7d3aee4b0</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="str"/>
       <x:c r="H63" s="1" t="n">
-        <x:v>1169</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I63" s="1" t="n">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J63" s="1" t="n">
-        <x:v>322</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K63" s="1" t="n">
-        <x:v>413</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L63" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M63" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N63" s="1" t="n">
         <x:v>8</x:v>
@@ -3057,31 +2941,29 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E64" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_31.png</x:v>
       </x:c>
       <x:c r="F64" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G64" s="1" t="str">
-        <x:v>167:627</x:v>
-      </x:c>
+        <x:v>b648cbc99eab0b9c2ef17c0cd77d4425102052f69f245e08100c98092beaea1c</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="str"/>
       <x:c r="H64" s="1" t="n">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I64" s="1" t="n">
-        <x:v>625</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J64" s="1" t="n">
-        <x:v>351</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K64" s="1" t="n">
-        <x:v>289</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L64" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M64" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N64" s="1" t="n">
         <x:v>8</x:v>
@@ -3101,31 +2983,29 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E65" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_29.png</x:v>
       </x:c>
       <x:c r="F65" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G65" s="1" t="str">
-        <x:v>526:607</x:v>
-      </x:c>
+        <x:v>8ecf439eb03d16886b18de149bdce8c9cd893bd074f1b5f9c5b7057331cedf37</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="str"/>
       <x:c r="H65" s="1" t="n">
-        <x:v>394</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I65" s="1" t="n">
-        <x:v>605</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J65" s="1" t="n">
-        <x:v>357</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K65" s="1" t="n">
-        <x:v>308</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L65" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M65" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N65" s="1" t="n">
         <x:v>8</x:v>
@@ -3145,31 +3025,29 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E66" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_33.png</x:v>
       </x:c>
       <x:c r="F66" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G66" s="1" t="str">
-        <x:v>526:607</x:v>
-      </x:c>
+        <x:v>8ecf439eb03d16886b18de149bdce8c9cd893bd074f1b5f9c5b7057331cedf37</x:v>
+      </x:c>
+      <x:c r="G66" s="1" t="str"/>
       <x:c r="H66" s="1" t="n">
-        <x:v>394</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I66" s="1" t="n">
-        <x:v>605</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J66" s="1" t="n">
-        <x:v>357</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K66" s="1" t="n">
-        <x:v>308</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L66" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M66" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N66" s="1" t="n">
         <x:v>8</x:v>
@@ -3189,31 +3067,29 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E67" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_30.png</x:v>
       </x:c>
       <x:c r="F67" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G67" s="1" t="str">
-        <x:v>911:605</x:v>
-      </x:c>
+        <x:v>b207719798f4b1824496e6f2c4222a0b793b37e337a2504cb6b15555c9dfd55f</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="str"/>
       <x:c r="H67" s="1" t="n">
-        <x:v>796</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I67" s="1" t="n">
-        <x:v>603</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J67" s="1" t="n">
-        <x:v>334</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K67" s="1" t="n">
-        <x:v>331</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L67" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M67" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N67" s="1" t="n">
         <x:v>8</x:v>
@@ -3233,31 +3109,29 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E68" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_34.png</x:v>
       </x:c>
       <x:c r="F68" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G68" s="1" t="str">
-        <x:v>911:605</x:v>
-      </x:c>
+        <x:v>b207719798f4b1824496e6f2c4222a0b793b37e337a2504cb6b15555c9dfd55f</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="str"/>
       <x:c r="H68" s="1" t="n">
-        <x:v>796</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I68" s="1" t="n">
-        <x:v>603</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J68" s="1" t="n">
-        <x:v>334</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K68" s="1" t="n">
-        <x:v>331</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L68" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M68" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N68" s="1" t="n">
         <x:v>8</x:v>
@@ -3277,31 +3151,29 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E69" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/scenery_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_4.png</x:v>
       </x:c>
       <x:c r="F69" s="1" t="str">
-        <x:v>40e24e6518366676ce78de263bb55cf6e969db017af4715a3be14367f1f2fa23</x:v>
-      </x:c>
-      <x:c r="G69" s="1" t="str">
-        <x:v>1320:684</x:v>
-      </x:c>
+        <x:v>f7e75eb2df5fcd035241ffe8333bda62a8565b7a898ca523ed727f9ff6cf03a8</x:v>
+      </x:c>
+      <x:c r="G69" s="1" t="str"/>
       <x:c r="H69" s="1" t="n">
-        <x:v>1167</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I69" s="1" t="n">
-        <x:v>682</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J69" s="1" t="n">
-        <x:v>339</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K69" s="1" t="n">
-        <x:v>232</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L69" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M69" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N69" s="1" t="n">
         <x:v>8</x:v>
@@ -3321,31 +3193,29 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E70" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/boss_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_22.png</x:v>
       </x:c>
       <x:c r="F70" s="1" t="str">
-        <x:v>d4a770b9442e3d1ab15ed64bddc2d4164afef6156c5b32b4e84cfa439484c63d</x:v>
-      </x:c>
-      <x:c r="G70" s="1" t="str">
-        <x:v>409:65</x:v>
-      </x:c>
+        <x:v>ffa2e3fc8497d89c84c7210548baeb1bfe5b602ed996ddb6146a9c146fd937b9</x:v>
+      </x:c>
+      <x:c r="G70" s="1" t="str"/>
       <x:c r="H70" s="1" t="n">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I70" s="1" t="n">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J70" s="1" t="n">
-        <x:v>528</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K70" s="1" t="n">
-        <x:v>549</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L70" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M70" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N70" s="1" t="n">
         <x:v>8</x:v>
@@ -3365,31 +3235,29 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E71" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/boss_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_23.png</x:v>
       </x:c>
       <x:c r="F71" s="1" t="str">
-        <x:v>d4a770b9442e3d1ab15ed64bddc2d4164afef6156c5b32b4e84cfa439484c63d</x:v>
-      </x:c>
-      <x:c r="G71" s="1" t="str">
-        <x:v>897:36</x:v>
-      </x:c>
+        <x:v>ee43fe9c23332e4be63abf5e596a0d9df1721bad924f29facc6dafd9a54fe3ec</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="str"/>
       <x:c r="H71" s="1" t="n">
-        <x:v>653</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I71" s="1" t="n">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J71" s="1" t="n">
-        <x:v>501</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K71" s="1" t="n">
-        <x:v>577</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L71" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M71" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N71" s="1" t="n">
         <x:v>8</x:v>
@@ -3409,31 +3277,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E72" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/boss_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_24.png</x:v>
       </x:c>
       <x:c r="F72" s="1" t="str">
-        <x:v>d4a770b9442e3d1ab15ed64bddc2d4164afef6156c5b32b4e84cfa439484c63d</x:v>
-      </x:c>
-      <x:c r="G72" s="1" t="str">
-        <x:v>414:633</x:v>
-      </x:c>
+        <x:v>4c8157f8984f203572b8f553a4aa3f625e799bc335a73c695b4569212bd2d7cd</x:v>
+      </x:c>
+      <x:c r="G72" s="1" t="str"/>
       <x:c r="H72" s="1" t="n">
-        <x:v>58</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I72" s="1" t="n">
-        <x:v>631</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J72" s="1" t="n">
-        <x:v>595</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K72" s="1" t="n">
-        <x:v>577</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L72" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M72" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N72" s="1" t="n">
         <x:v>8</x:v>
@@ -3453,31 +3319,29 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E73" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/boss_sheet.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_25.png</x:v>
       </x:c>
       <x:c r="F73" s="1" t="str">
-        <x:v>d4a770b9442e3d1ab15ed64bddc2d4164afef6156c5b32b4e84cfa439484c63d</x:v>
-      </x:c>
-      <x:c r="G73" s="1" t="str">
-        <x:v>931:660</x:v>
-      </x:c>
+        <x:v>858d2648212896c02772802eb14202be19529e567aa84323569b086881b6befa</x:v>
+      </x:c>
+      <x:c r="G73" s="1" t="str"/>
       <x:c r="H73" s="1" t="n">
-        <x:v>662</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I73" s="1" t="n">
-        <x:v>658</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J73" s="1" t="n">
-        <x:v>527</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K73" s="1" t="n">
-        <x:v>544</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L73" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M73" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N73" s="1" t="n">
         <x:v>8</x:v>
@@ -3497,31 +3361,29 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E74" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_36.png</x:v>
       </x:c>
       <x:c r="F74" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G74" s="1" t="str">
-        <x:v>160:143</x:v>
-      </x:c>
+        <x:v>a60b6d747b847c55f21c55caa2878abf6a736c7019da21a01ce8fd0a7975ff9f</x:v>
+      </x:c>
+      <x:c r="G74" s="1" t="str"/>
       <x:c r="H74" s="1" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I74" s="1" t="n">
-        <x:v>141</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J74" s="1" t="n">
-        <x:v>391</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K74" s="1" t="n">
-        <x:v>371</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L74" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M74" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N74" s="1" t="n">
         <x:v>8</x:v>
@@ -3541,31 +3403,29 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E75" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_38.png</x:v>
       </x:c>
       <x:c r="F75" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G75" s="1" t="str">
-        <x:v>579:150</x:v>
-      </x:c>
+        <x:v>f2f97da73dcbb0181537d950d966bbe3103b08ef9411ac070c372c0713abfea3</x:v>
+      </x:c>
+      <x:c r="G75" s="1" t="str"/>
       <x:c r="H75" s="1" t="n">
-        <x:v>403</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I75" s="1" t="n">
-        <x:v>148</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J75" s="1" t="n">
-        <x:v>369</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K75" s="1" t="n">
-        <x:v>361</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L75" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M75" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N75" s="1" t="n">
         <x:v>8</x:v>
@@ -3585,31 +3445,29 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_40.png</x:v>
       </x:c>
       <x:c r="F76" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G76" s="1" t="str">
-        <x:v>927:115</x:v>
-      </x:c>
+        <x:v>e9efb43e4c95512de5cf8faa0979b8bf1a33f6f16a1b7167c5f5c9b3b7245311</x:v>
+      </x:c>
+      <x:c r="G76" s="1" t="str"/>
       <x:c r="H76" s="1" t="n">
-        <x:v>770</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I76" s="1" t="n">
-        <x:v>113</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J76" s="1" t="n">
-        <x:v>376</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K76" s="1" t="n">
-        <x:v>399</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L76" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M76" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N76" s="1" t="n">
         <x:v>8</x:v>
@@ -3629,31 +3487,29 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E77" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_42.png</x:v>
       </x:c>
       <x:c r="F77" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G77" s="1" t="str">
-        <x:v>1322:151</x:v>
-      </x:c>
+        <x:v>7fd95c843710d2467ee542cc56c6f3796f55f4376bf1f5a0911171dd01218841</x:v>
+      </x:c>
+      <x:c r="G77" s="1" t="str"/>
       <x:c r="H77" s="1" t="n">
-        <x:v>1157</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I77" s="1" t="n">
-        <x:v>149</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J77" s="1" t="n">
-        <x:v>375</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K77" s="1" t="n">
-        <x:v>363</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L77" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M77" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N77" s="1" t="n">
         <x:v>8</x:v>
@@ -3673,31 +3529,29 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E78" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_44.png</x:v>
       </x:c>
       <x:c r="F78" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G78" s="1" t="str">
-        <x:v>224:587</x:v>
-      </x:c>
+        <x:v>8e48087e0ab87901adcb22c33b23b22db189db47d082ee8f29c3483e771e39f0</x:v>
+      </x:c>
+      <x:c r="G78" s="1" t="str"/>
       <x:c r="H78" s="1" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I78" s="1" t="n">
-        <x:v>585</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J78" s="1" t="n">
-        <x:v>401</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K78" s="1" t="n">
-        <x:v>348</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L78" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M78" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N78" s="1" t="n">
         <x:v>8</x:v>
@@ -3717,31 +3571,29 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_46.png</x:v>
       </x:c>
       <x:c r="F79" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G79" s="1" t="str">
-        <x:v>593:540</x:v>
-      </x:c>
+        <x:v>693ed3ca5eaf0dfb073d29785d5bdcaeaa168c72cbe231703f09b67bd131df87</x:v>
+      </x:c>
+      <x:c r="G79" s="1" t="str"/>
       <x:c r="H79" s="1" t="n">
-        <x:v>405</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I79" s="1" t="n">
-        <x:v>538</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J79" s="1" t="n">
-        <x:v>370</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K79" s="1" t="n">
-        <x:v>397</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L79" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M79" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N79" s="1" t="n">
         <x:v>8</x:v>
@@ -3761,31 +3613,29 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E80" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_48.png</x:v>
       </x:c>
       <x:c r="F80" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G80" s="1" t="str">
-        <x:v>920:569</x:v>
-      </x:c>
+        <x:v>82127138ee12a342ab5af1269f1fea8ceb1cdddf045f929cbd00066b77bb4fab</x:v>
+      </x:c>
+      <x:c r="G80" s="1" t="str"/>
       <x:c r="H80" s="1" t="n">
-        <x:v>777</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I80" s="1" t="n">
-        <x:v>567</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J80" s="1" t="n">
-        <x:v>399</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K80" s="1" t="n">
-        <x:v>367</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L80" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M80" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N80" s="1" t="n">
         <x:v>8</x:v>
@@ -3805,31 +3655,29 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E81" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_50.png</x:v>
       </x:c>
       <x:c r="F81" s="1" t="str">
-        <x:v>c23c212ca065e45bbe2a2310bdbfc744c063942e7c4faeee8963420fe78b91dd</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="str">
-        <x:v>1312:596</x:v>
-      </x:c>
+        <x:v>d946250b58c516f95e0ae8b9760fcc6fdf1f6eaddc2f46714df40430197c70eb</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="str"/>
       <x:c r="H81" s="1" t="n">
-        <x:v>1156</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I81" s="1" t="n">
-        <x:v>594</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J81" s="1" t="n">
-        <x:v>371</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K81" s="1" t="n">
-        <x:v>340</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L81" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M81" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N81" s="1" t="n">
         <x:v>8</x:v>
@@ -3849,31 +3697,29 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E82" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_37.png</x:v>
       </x:c>
       <x:c r="F82" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G82" s="1" t="str">
-        <x:v>211:215</x:v>
-      </x:c>
+        <x:v>71fd7ac29c78649c3ec20e9c67a400e1a6db27da27ba4a5ee80ec001094bce5d</x:v>
+      </x:c>
+      <x:c r="G82" s="1" t="str"/>
       <x:c r="H82" s="1" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I82" s="1" t="n">
-        <x:v>213</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J82" s="1" t="n">
-        <x:v>402</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K82" s="1" t="n">
-        <x:v>303</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L82" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M82" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N82" s="1" t="n">
         <x:v>8</x:v>
@@ -3893,31 +3739,29 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_39.png</x:v>
       </x:c>
       <x:c r="F83" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G83" s="1" t="str">
-        <x:v>605:203</x:v>
-      </x:c>
+        <x:v>816446b7f622cac60a26748c7ad3502fa76fbb39686b60c5a10344bd7c4258ae</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="str"/>
       <x:c r="H83" s="1" t="n">
-        <x:v>418</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I83" s="1" t="n">
-        <x:v>201</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J83" s="1" t="n">
-        <x:v>343</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K83" s="1" t="n">
-        <x:v>315</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L83" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M83" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N83" s="1" t="n">
         <x:v>8</x:v>
@@ -3937,31 +3781,29 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E84" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_41.png</x:v>
       </x:c>
       <x:c r="F84" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G84" s="1" t="str">
-        <x:v>908:183</x:v>
-      </x:c>
+        <x:v>efb8f37399281bc9fe07971384ca6ab0bf40f199917f137b07e2a830af75614c</x:v>
+      </x:c>
+      <x:c r="G84" s="1" t="str"/>
       <x:c r="H84" s="1" t="n">
-        <x:v>764</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I84" s="1" t="n">
-        <x:v>181</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J84" s="1" t="n">
-        <x:v>388</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K84" s="1" t="n">
-        <x:v>336</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L84" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M84" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N84" s="1" t="n">
         <x:v>8</x:v>
@@ -3981,31 +3823,29 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E85" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_43.png</x:v>
       </x:c>
       <x:c r="F85" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G85" s="1" t="str">
-        <x:v>1270:211</x:v>
-      </x:c>
+        <x:v>9cde2abd17b546fff7a02fb94bb804423f8e143373ecb83d3b2d3ca062ae9eb4</x:v>
+      </x:c>
+      <x:c r="G85" s="1" t="str"/>
       <x:c r="H85" s="1" t="n">
-        <x:v>1158</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I85" s="1" t="n">
-        <x:v>209</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J85" s="1" t="n">
-        <x:v>369</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K85" s="1" t="n">
-        <x:v>321</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L85" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M85" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N85" s="1" t="n">
         <x:v>8</x:v>
@@ -4025,31 +3865,29 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E86" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_45.png</x:v>
       </x:c>
       <x:c r="F86" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G86" s="1" t="str">
-        <x:v>222:566|411:651</x:v>
-      </x:c>
+        <x:v>ad5096d1ce3b8da27ec1c003bf90d0016d5b67eb464b38b55cbc74a37063a511</x:v>
+      </x:c>
+      <x:c r="G86" s="1" t="str"/>
       <x:c r="H86" s="1" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I86" s="1" t="n">
-        <x:v>564</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J86" s="1" t="n">
-        <x:v>421</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K86" s="1" t="n">
-        <x:v>325</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L86" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M86" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N86" s="1" t="n">
         <x:v>8</x:v>
@@ -4069,31 +3907,29 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E87" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_47.png</x:v>
       </x:c>
       <x:c r="F87" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G87" s="1" t="str">
-        <x:v>554:576|738:645</x:v>
-      </x:c>
+        <x:v>355c70631488cb95ae429ed1292ecd9aa4d5ec0020edc91c26a7627d39d574f4</x:v>
+      </x:c>
+      <x:c r="G87" s="1" t="str"/>
       <x:c r="H87" s="1" t="n">
-        <x:v>401</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I87" s="1" t="n">
-        <x:v>574</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J87" s="1" t="n">
-        <x:v>385</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K87" s="1" t="n">
-        <x:v>313</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L87" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M87" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N87" s="1" t="n">
         <x:v>8</x:v>
@@ -4113,31 +3949,29 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E88" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_49.png</x:v>
       </x:c>
       <x:c r="F88" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G88" s="1" t="str">
-        <x:v>934:564</x:v>
-      </x:c>
+        <x:v>4fb88a4fcdb87bca287803aee933c00a46a5a69d28683da0d3a14cbe515ff896</x:v>
+      </x:c>
+      <x:c r="G88" s="1" t="str"/>
       <x:c r="H88" s="1" t="n">
-        <x:v>771</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I88" s="1" t="n">
-        <x:v>562</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J88" s="1" t="n">
-        <x:v>325</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K88" s="1" t="n">
-        <x:v>328</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L88" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M88" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N88" s="1" t="n">
         <x:v>8</x:v>
@@ -4157,31 +3991,29 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E89" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/evoB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_51.png</x:v>
       </x:c>
       <x:c r="F89" s="1" t="str">
-        <x:v>17b4b75d04464713b692d8a2e721a46969812a46972695fd1811511fde71cf73</x:v>
-      </x:c>
-      <x:c r="G89" s="1" t="str">
-        <x:v>1312:591</x:v>
-      </x:c>
+        <x:v>d2a00aeecade7b3bf174b4a0b8dba42f5e04e277fb08d57c2add8d760973d5df</x:v>
+      </x:c>
+      <x:c r="G89" s="1" t="str"/>
       <x:c r="H89" s="1" t="n">
-        <x:v>1134</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I89" s="1" t="n">
-        <x:v>589</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J89" s="1" t="n">
-        <x:v>390</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K89" s="1" t="n">
-        <x:v>302</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L89" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M89" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N89" s="1" t="n">
         <x:v>8</x:v>
@@ -4201,31 +4033,29 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="E90" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_52.png</x:v>
       </x:c>
       <x:c r="F90" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G90" s="1" t="str">
-        <x:v>259:42|175:52|266:125|242:199</x:v>
-      </x:c>
+        <x:v>75de59b91263328956f78e55ccc6f347598f42d748bd069e2751702afd441ec1</x:v>
+      </x:c>
+      <x:c r="G90" s="1" t="str"/>
       <x:c r="H90" s="1" t="n">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I90" s="1" t="n">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J90" s="1" t="n">
-        <x:v>278</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K90" s="1" t="n">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L90" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M90" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N90" s="1" t="n">
         <x:v>8</x:v>
@@ -4245,31 +4075,29 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E91" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_53.png</x:v>
       </x:c>
       <x:c r="F91" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G91" s="1" t="str">
-        <x:v>465:37|577:97</x:v>
-      </x:c>
+        <x:v>2723163dba81b12a1f1fbd44d137065fa7fd7fd1c902c849bcfa928fb8a0b275</x:v>
+      </x:c>
+      <x:c r="G91" s="1" t="str"/>
       <x:c r="H91" s="1" t="n">
-        <x:v>346</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I91" s="1" t="n">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J91" s="1" t="n">
-        <x:v>265</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K91" s="1" t="n">
-        <x:v>265</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L91" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M91" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N91" s="1" t="n">
         <x:v>8</x:v>
@@ -4289,31 +4117,29 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E92" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_54.png</x:v>
       </x:c>
       <x:c r="F92" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G92" s="1" t="str">
-        <x:v>704:38|790:62|665:129|857:242</x:v>
-      </x:c>
+        <x:v>6206c232dfd63188b7bbdb84c3d94071db2e74ddb3df1ed99f8f8b9affc9bfb3</x:v>
+      </x:c>
+      <x:c r="G92" s="1" t="str"/>
       <x:c r="H92" s="1" t="n">
-        <x:v>652</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I92" s="1" t="n">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J92" s="1" t="n">
-        <x:v>276</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K92" s="1" t="n">
-        <x:v>260</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L92" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M92" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N92" s="1" t="n">
         <x:v>8</x:v>
@@ -4333,31 +4159,29 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E93" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_55.png</x:v>
       </x:c>
       <x:c r="F93" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G93" s="1" t="str">
-        <x:v>1193:39|1042:56</x:v>
-      </x:c>
+        <x:v>e917f91d669be1f685292076856d9a587ee45848d942acf1ab911a843aa5e45b</x:v>
+      </x:c>
+      <x:c r="G93" s="1" t="str"/>
       <x:c r="H93" s="1" t="n">
-        <x:v>952</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I93" s="1" t="n">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J93" s="1" t="n">
-        <x:v>279</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K93" s="1" t="n">
-        <x:v>260</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L93" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M93" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N93" s="1" t="n">
         <x:v>8</x:v>
@@ -4377,31 +4201,29 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E94" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_56.png</x:v>
       </x:c>
       <x:c r="F94" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G94" s="1" t="str">
-        <x:v>142:341|276:383|35:465</x:v>
-      </x:c>
+        <x:v>3288231a0912fa3c694faf8c4d2de0d4b1f14d822322ed762d04ad4d8e54caea</x:v>
+      </x:c>
+      <x:c r="G94" s="1" t="str"/>
       <x:c r="H94" s="1" t="n">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I94" s="1" t="n">
-        <x:v>339</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J94" s="1" t="n">
-        <x:v>276</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K94" s="1" t="n">
-        <x:v>264</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L94" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M94" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N94" s="1" t="n">
         <x:v>8</x:v>
@@ -4421,31 +4243,29 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E95" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_57.png</x:v>
       </x:c>
       <x:c r="F95" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G95" s="1" t="str">
-        <x:v>483:331|568:356|385:370|582:530|353:550</x:v>
-      </x:c>
+        <x:v>0c3716059b5e9ba33ccc7f9851e38118bf76b847b57c67efddd9a04236a34213</x:v>
+      </x:c>
+      <x:c r="G95" s="1" t="str"/>
       <x:c r="H95" s="1" t="n">
-        <x:v>342</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I95" s="1" t="n">
-        <x:v>329</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J95" s="1" t="n">
-        <x:v>255</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K95" s="1" t="n">
-        <x:v>275</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L95" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M95" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N95" s="1" t="n">
         <x:v>8</x:v>
@@ -4465,31 +4285,29 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E96" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_58.png</x:v>
       </x:c>
       <x:c r="F96" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G96" s="1" t="str">
-        <x:v>838:329|762:337|695:402|672:444</x:v>
-      </x:c>
+        <x:v>a2c436017c486d007fd97128ca3f772c15319adff6bbe8fde53f81577d49152f</x:v>
+      </x:c>
+      <x:c r="G96" s="1" t="str"/>
       <x:c r="H96" s="1" t="n">
-        <x:v>665</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I96" s="1" t="n">
-        <x:v>327</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J96" s="1" t="n">
-        <x:v>248</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K96" s="1" t="n">
-        <x:v>289</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L96" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M96" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N96" s="1" t="n">
         <x:v>8</x:v>
@@ -4509,31 +4327,29 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="E97" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_59.png</x:v>
       </x:c>
       <x:c r="F97" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G97" s="1" t="str">
-        <x:v>1096:337|1187:406|980:527</x:v>
-      </x:c>
+        <x:v>5caac403093308a9fb1b52450e7e1edc625c9f80751aa20068fc3ebd23fbf40e</x:v>
+      </x:c>
+      <x:c r="G97" s="1" t="str"/>
       <x:c r="H97" s="1" t="n">
-        <x:v>952</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I97" s="1" t="n">
-        <x:v>335</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J97" s="1" t="n">
-        <x:v>277</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K97" s="1" t="n">
-        <x:v>275</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L97" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M97" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N97" s="1" t="n">
         <x:v>8</x:v>
@@ -4553,31 +4369,29 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E98" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_60.png</x:v>
       </x:c>
       <x:c r="F98" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G98" s="1" t="str">
-        <x:v>91:649</x:v>
-      </x:c>
+        <x:v>9e78e42d9adb2fa001204ce09cc3b4b75c2f26670193832749ef9b4b01467847</x:v>
+      </x:c>
+      <x:c r="G98" s="1" t="str"/>
       <x:c r="H98" s="1" t="n">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I98" s="1" t="n">
-        <x:v>647</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J98" s="1" t="n">
-        <x:v>265</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K98" s="1" t="n">
-        <x:v>255</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L98" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M98" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N98" s="1" t="n">
         <x:v>8</x:v>
@@ -4597,31 +4411,29 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E99" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_61.png</x:v>
       </x:c>
       <x:c r="F99" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G99" s="1" t="str">
-        <x:v>463:651|434:662|504:662|355:701</x:v>
-      </x:c>
+        <x:v>8e7b89fb6fd0340bee48c78203f660737f5f30dca76515cac0ced2aebbf9c35a</x:v>
+      </x:c>
+      <x:c r="G99" s="1" t="str"/>
       <x:c r="H99" s="1" t="n">
-        <x:v>324</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I99" s="1" t="n">
-        <x:v>649</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J99" s="1" t="n">
-        <x:v>293</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K99" s="1" t="n">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L99" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M99" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N99" s="1" t="n">
         <x:v>8</x:v>
@@ -4641,31 +4453,29 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E100" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_62.png</x:v>
       </x:c>
       <x:c r="F100" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G100" s="1" t="str">
-        <x:v>786:648|873:659|684:693|884:748</x:v>
-      </x:c>
+        <x:v>cb5323aed96959daaf27bdc7852c4a695cadc2ba5e767bd19faf6524c2e77dd3</x:v>
+      </x:c>
+      <x:c r="G100" s="1" t="str"/>
       <x:c r="H100" s="1" t="n">
-        <x:v>660</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I100" s="1" t="n">
-        <x:v>646</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J100" s="1" t="n">
-        <x:v>248</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K100" s="1" t="n">
-        <x:v>267</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L100" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M100" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N100" s="1" t="n">
         <x:v>8</x:v>
@@ -4685,31 +4495,29 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="E101" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_63.png</x:v>
       </x:c>
       <x:c r="F101" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G101" s="1" t="str">
-        <x:v>1084:653|1025:679|983:723</x:v>
-      </x:c>
+        <x:v>96eda17c0fafe85e76cba173c24e494503e76d45048b579435bc51670ee39da2</x:v>
+      </x:c>
+      <x:c r="G101" s="1" t="str"/>
       <x:c r="H101" s="1" t="n">
-        <x:v>961</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I101" s="1" t="n">
-        <x:v>651</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J101" s="1" t="n">
-        <x:v>260</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K101" s="1" t="n">
-        <x:v>263</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L101" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M101" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N101" s="1" t="n">
         <x:v>8</x:v>
@@ -4729,31 +4537,29 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E102" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_64.png</x:v>
       </x:c>
       <x:c r="F102" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G102" s="1" t="str">
-        <x:v>136:927</x:v>
-      </x:c>
+        <x:v>7dbce69c648a2a89f623442e3857d94b8b760e470ed164c1e9086446bee20560</x:v>
+      </x:c>
+      <x:c r="G102" s="1" t="str"/>
       <x:c r="H102" s="1" t="n">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I102" s="1" t="n">
-        <x:v>925</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J102" s="1" t="n">
-        <x:v>251</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K102" s="1" t="n">
-        <x:v>278</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L102" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M102" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N102" s="1" t="n">
         <x:v>8</x:v>
@@ -4773,31 +4579,29 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E103" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_65.png</x:v>
       </x:c>
       <x:c r="F103" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G103" s="1" t="str">
-        <x:v>439:978|494:1068</x:v>
-      </x:c>
+        <x:v>f58f789ab347f0cd9f12b61d58fd4ca4da2368adc47cd60420d4aa6b2872c8d8</x:v>
+      </x:c>
+      <x:c r="G103" s="1" t="str"/>
       <x:c r="H103" s="1" t="n">
-        <x:v>317</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I103" s="1" t="n">
-        <x:v>976</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J103" s="1" t="n">
-        <x:v>305</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K103" s="1" t="n">
-        <x:v>178</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L103" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M103" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N103" s="1" t="n">
         <x:v>8</x:v>
@@ -4817,31 +4621,29 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E104" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_66.png</x:v>
       </x:c>
       <x:c r="F104" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G104" s="1" t="str">
-        <x:v>773:950</x:v>
-      </x:c>
+        <x:v>a355b9aa47fac5596d799e30618b4d2b312c6ef7b48f3b52abb48e0b905a5319</x:v>
+      </x:c>
+      <x:c r="G104" s="1" t="str"/>
       <x:c r="H104" s="1" t="n">
-        <x:v>661</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I104" s="1" t="n">
-        <x:v>948</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J104" s="1" t="n">
-        <x:v>259</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K104" s="1" t="n">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L104" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M104" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N104" s="1" t="n">
         <x:v>8</x:v>
@@ -4861,31 +4663,29 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E105" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksA.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_67.png</x:v>
       </x:c>
       <x:c r="F105" s="1" t="str">
-        <x:v>728d46d99a6d34a4175370ad781ebc8a3f5d092741758adf655400d4de14587f</x:v>
-      </x:c>
-      <x:c r="G105" s="1" t="str">
-        <x:v>1150:943|1004:1017|1196:1019</x:v>
-      </x:c>
+        <x:v>d6eada5e92157bd2d9452a78d06828aaa02e892f5c8dacc242d5a4d89c3844f6</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="str"/>
       <x:c r="H105" s="1" t="n">
-        <x:v>971</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I105" s="1" t="n">
-        <x:v>941</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J105" s="1" t="n">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K105" s="1" t="n">
-        <x:v>267</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L105" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M105" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N105" s="1" t="n">
         <x:v>8</x:v>
@@ -4905,31 +4705,29 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="E106" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_68.png</x:v>
       </x:c>
       <x:c r="F106" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G106" s="1" t="str">
-        <x:v>126:48</x:v>
-      </x:c>
+        <x:v>11f472567644db636b11865dcd8e29708ea14befa2728e3dec5d5deaaf3c2b83</x:v>
+      </x:c>
+      <x:c r="G106" s="1" t="str"/>
       <x:c r="H106" s="1" t="n">
-        <x:v>42</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I106" s="1" t="n">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J106" s="1" t="n">
-        <x:v>266</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K106" s="1" t="n">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L106" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M106" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N106" s="1" t="n">
         <x:v>8</x:v>
@@ -4949,31 +4747,29 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E107" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_69.png</x:v>
       </x:c>
       <x:c r="F107" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G107" s="1" t="str">
-        <x:v>435:46</x:v>
-      </x:c>
+        <x:v>fe661da43bc6926ca5d315fe616a04ecb2a37f56efb9a715746248ce8b18793b</x:v>
+      </x:c>
+      <x:c r="G107" s="1" t="str"/>
       <x:c r="H107" s="1" t="n">
-        <x:v>337</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I107" s="1" t="n">
-        <x:v>44</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J107" s="1" t="n">
-        <x:v>292</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K107" s="1" t="n">
-        <x:v>266</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L107" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M107" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N107" s="1" t="n">
         <x:v>8</x:v>
@@ -4993,31 +4789,29 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E108" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_70.png</x:v>
       </x:c>
       <x:c r="F108" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G108" s="1" t="str">
-        <x:v>797:52|713:78|851:96|916:165|922:197</x:v>
-      </x:c>
+        <x:v>754c7498ee71802d801eac3ebbfdf0d6ac8835b4e8fdc8199eb2c4a397e7cfde</x:v>
+      </x:c>
+      <x:c r="G108" s="1" t="str"/>
       <x:c r="H108" s="1" t="n">
-        <x:v>653</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I108" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J108" s="1" t="n">
-        <x:v>278</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K108" s="1" t="n">
-        <x:v>268</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L108" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M108" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N108" s="1" t="n">
         <x:v>8</x:v>
@@ -5037,31 +4831,29 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E109" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_71.png</x:v>
       </x:c>
       <x:c r="F109" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G109" s="1" t="str">
-        <x:v>1099:39|1172:66|1023:77|1201:90</x:v>
-      </x:c>
+        <x:v>ddf1daf0ce9eb9b704089c15ff66099ca39fea1bb1ef66141d2c1861d0abdafa</x:v>
+      </x:c>
+      <x:c r="G109" s="1" t="str"/>
       <x:c r="H109" s="1" t="n">
-        <x:v>964</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I109" s="1" t="n">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J109" s="1" t="n">
-        <x:v>250</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K109" s="1" t="n">
-        <x:v>282</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L109" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M109" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N109" s="1" t="n">
         <x:v>8</x:v>
@@ -5081,31 +4873,29 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="E110" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_72.png</x:v>
       </x:c>
       <x:c r="F110" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G110" s="1" t="str">
-        <x:v>231:357</x:v>
-      </x:c>
+        <x:v>ece77524b1073d7fa1eeea4c719a7dffc1b89d2d32120c29bc25c4451302ff4f</x:v>
+      </x:c>
+      <x:c r="G110" s="1" t="str"/>
       <x:c r="H110" s="1" t="n">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I110" s="1" t="n">
-        <x:v>355</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J110" s="1" t="n">
-        <x:v>272</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K110" s="1" t="n">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L110" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M110" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N110" s="1" t="n">
         <x:v>8</x:v>
@@ -5125,31 +4915,29 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="E111" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_73.png</x:v>
       </x:c>
       <x:c r="F111" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G111" s="1" t="str">
-        <x:v>354:340</x:v>
-      </x:c>
+        <x:v>306ae93203ed9c7b9a0cacdb06a7d44bb5a54652e95a2017ba6ad53a866f3de4</x:v>
+      </x:c>
+      <x:c r="G111" s="1" t="str"/>
       <x:c r="H111" s="1" t="n">
-        <x:v>342</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I111" s="1" t="n">
-        <x:v>338</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J111" s="1" t="n">
-        <x:v>268</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K111" s="1" t="n">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L111" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M111" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N111" s="1" t="n">
         <x:v>8</x:v>
@@ -5169,31 +4957,29 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="E112" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_74.png</x:v>
       </x:c>
       <x:c r="F112" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G112" s="1" t="str">
-        <x:v>840:352|684:379|896:398</x:v>
-      </x:c>
+        <x:v>843f13e3cbac43816a7be8c0c2d2e475c2b93258ca0b032ef2abe0a828e9f352</x:v>
+      </x:c>
+      <x:c r="G112" s="1" t="str"/>
       <x:c r="H112" s="1" t="n">
-        <x:v>635</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I112" s="1" t="n">
-        <x:v>350</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J112" s="1" t="n">
-        <x:v>295</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K112" s="1" t="n">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L112" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M112" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N112" s="1" t="n">
         <x:v>8</x:v>
@@ -5213,31 +4999,29 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E113" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_75.png</x:v>
       </x:c>
       <x:c r="F113" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G113" s="1" t="str">
-        <x:v>1054:355|1200:366|1168:387|1177:412|1194:468|1146:483</x:v>
-      </x:c>
+        <x:v>f3c64f3c211937ef1bf7b29ffe6caf568c9a01a175a6313a377b93015fff09e6</x:v>
+      </x:c>
+      <x:c r="G113" s="1" t="str"/>
       <x:c r="H113" s="1" t="n">
-        <x:v>951</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I113" s="1" t="n">
-        <x:v>353</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J113" s="1" t="n">
-        <x:v>282</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K113" s="1" t="n">
-        <x:v>251</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L113" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M113" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N113" s="1" t="n">
         <x:v>8</x:v>
@@ -5257,31 +5041,29 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E114" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_76.png</x:v>
       </x:c>
       <x:c r="F114" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G114" s="1" t="str">
-        <x:v>101:631|165:631|204:668|59:771|105:833|142:840</x:v>
-      </x:c>
+        <x:v>0191b60f4706c2266d18df4e9dba76c4e3401e499fc057f383b2052920f85b2f</x:v>
+      </x:c>
+      <x:c r="G114" s="1" t="str"/>
       <x:c r="H114" s="1" t="n">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I114" s="1" t="n">
-        <x:v>629</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J114" s="1" t="n">
-        <x:v>293</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K114" s="1" t="n">
-        <x:v>279</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L114" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M114" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N114" s="1" t="n">
         <x:v>8</x:v>
@@ -5301,31 +5083,29 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="E115" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_77.png</x:v>
       </x:c>
       <x:c r="F115" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G115" s="1" t="str">
-        <x:v>357:633|603:718|617:754</x:v>
-      </x:c>
+        <x:v>03ff707cfcd86c74859b151dbd43fdeeebcc4ff97d721913cb659fa6b1c7ac47</x:v>
+      </x:c>
+      <x:c r="G115" s="1" t="str"/>
       <x:c r="H115" s="1" t="n">
-        <x:v>347</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I115" s="1" t="n">
-        <x:v>631</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J115" s="1" t="n">
-        <x:v>281</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K115" s="1" t="n">
-        <x:v>268</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L115" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M115" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N115" s="1" t="n">
         <x:v>8</x:v>
@@ -5345,31 +5125,29 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E116" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_78.png</x:v>
       </x:c>
       <x:c r="F116" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G116" s="1" t="str">
-        <x:v>731:626</x:v>
-      </x:c>
+        <x:v>d010b8e7e604587c129908b435016c15e3ad2f4c989615134b45fa382378e797</x:v>
+      </x:c>
+      <x:c r="G116" s="1" t="str"/>
       <x:c r="H116" s="1" t="n">
-        <x:v>642</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I116" s="1" t="n">
-        <x:v>624</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J116" s="1" t="n">
-        <x:v>289</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K116" s="1" t="n">
-        <x:v>294</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L116" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M116" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N116" s="1" t="n">
         <x:v>8</x:v>
@@ -5389,31 +5167,29 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E117" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_79.png</x:v>
       </x:c>
       <x:c r="F117" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G117" s="1" t="str">
-        <x:v>1187:661|1030:707|1000:735</x:v>
-      </x:c>
+        <x:v>bbdcbbb27269822e5d0b03ee11a670fd0e73bbf3ec6fed66fdae33d3a63f83df</x:v>
+      </x:c>
+      <x:c r="G117" s="1" t="str"/>
       <x:c r="H117" s="1" t="n">
-        <x:v>984</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I117" s="1" t="n">
-        <x:v>659</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J117" s="1" t="n">
-        <x:v>232</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K117" s="1" t="n">
-        <x:v>254</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L117" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M117" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N117" s="1" t="n">
         <x:v>8</x:v>
@@ -5433,31 +5209,29 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E118" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_80.png</x:v>
       </x:c>
       <x:c r="F118" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G118" s="1" t="str">
-        <x:v>260:924|199:942|312:983|297:1020</x:v>
-      </x:c>
+        <x:v>e0123d2c9e6576a7105896162d707fffeeea46f2d73615d1233b640926be45f0</x:v>
+      </x:c>
+      <x:c r="G118" s="1" t="str"/>
       <x:c r="H118" s="1" t="n">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I118" s="1" t="n">
-        <x:v>922</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J118" s="1" t="n">
-        <x:v>299</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K118" s="1" t="n">
-        <x:v>294</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L118" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M118" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N118" s="1" t="n">
         <x:v>8</x:v>
@@ -5477,31 +5251,29 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E119" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_81.png</x:v>
       </x:c>
       <x:c r="F119" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G119" s="1" t="str">
-        <x:v>483:960|566:972</x:v>
-      </x:c>
+        <x:v>a848759639e3d51a6c0431ba9c0cf1878adb3a355fc1950dd499217ba7b6c3b5</x:v>
+      </x:c>
+      <x:c r="G119" s="1" t="str"/>
       <x:c r="H119" s="1" t="n">
-        <x:v>320</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I119" s="1" t="n">
-        <x:v>958</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J119" s="1" t="n">
-        <x:v>315</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K119" s="1" t="n">
-        <x:v>256</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L119" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M119" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N119" s="1" t="n">
         <x:v>8</x:v>
@@ -5521,31 +5293,29 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E120" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_82.png</x:v>
       </x:c>
       <x:c r="F120" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G120" s="1" t="str">
-        <x:v>766:949|659:966|693:1111|707:1149</x:v>
-      </x:c>
+        <x:v>e16721c21b9f637142ce984fe76d6728d1958471df29b33de2da602b507aab2f</x:v>
+      </x:c>
+      <x:c r="G120" s="1" t="str"/>
       <x:c r="H120" s="1" t="n">
-        <x:v>643</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I120" s="1" t="n">
-        <x:v>947</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J120" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K120" s="1" t="n">
-        <x:v>264</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L120" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M120" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N120" s="1" t="n">
         <x:v>8</x:v>
@@ -5565,31 +5335,29 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E121" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/perksB.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/frame_83.png</x:v>
       </x:c>
       <x:c r="F121" s="1" t="str">
-        <x:v>c86c19b27219843d785bb8992476c2ebc3763ebbb3562aaaa630a6dfd9e1245a</x:v>
-      </x:c>
-      <x:c r="G121" s="1" t="str">
-        <x:v>1166:953|1063:958|1194:975</x:v>
-      </x:c>
+        <x:v>f20d120ade2c1cd2f150fae2b680fbecdfb488467dfe7788d8ca17210131a121</x:v>
+      </x:c>
+      <x:c r="G121" s="1" t="str"/>
       <x:c r="H121" s="1" t="n">
-        <x:v>952</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I121" s="1" t="n">
-        <x:v>951</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J121" s="1" t="n">
-        <x:v>278</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K121" s="1" t="n">
-        <x:v>264</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L121" s="1" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="M121" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N121" s="1" t="n">
         <x:v>8</x:v>
@@ -5609,10 +5377,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E122" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/home_background.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_85.png</x:v>
       </x:c>
       <x:c r="F122" s="1" t="str">
-        <x:v>4cc8de79c57c5ed3e1a5230d82899d452c30aaacc3944baaa005885d9fc611fa</x:v>
+        <x:v>6263f65e6d838e829c48046cc32e5ad3ae3f3396be3b2897d1dd748e179264d0</x:v>
       </x:c>
       <x:c r="G122" s="1" t="str"/>
       <x:c r="H122" s="1" t="n">
@@ -5631,7 +5399,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M122" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N122" s="1" t="n">
         <x:v>0</x:v>
@@ -5651,10 +5419,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E123" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/loading_background.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_86.png</x:v>
       </x:c>
       <x:c r="F123" s="1" t="str">
-        <x:v>332e843861a45628cf1dd461accf4aa73f8eb43db961ce4111a36dc164844cb3</x:v>
+        <x:v>92115092a66ce62164c551e4d20de9e16f0671fd6e553eab310209ba72c4c5ca</x:v>
       </x:c>
       <x:c r="G123" s="1" t="str"/>
       <x:c r="H123" s="1" t="n">
@@ -5673,7 +5441,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M123" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N123" s="1" t="n">
         <x:v>0</x:v>
@@ -5693,10 +5461,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E124" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/ground_tile.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_121.png</x:v>
       </x:c>
       <x:c r="F124" s="1" t="str">
-        <x:v>6da3bdd707b3a991abe224f391c0b0df9edd0fc19e98184fdee2d4ea6fd93fb1</x:v>
+        <x:v>ddada5042045d532ac6eac9adff15b452157dde5ada9232da2131327028887c0</x:v>
       </x:c>
       <x:c r="G124" s="1" t="str"/>
       <x:c r="H124" s="1" t="n">
@@ -5715,7 +5483,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M124" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N124" s="1" t="n">
         <x:v>0</x:v>
@@ -5735,10 +5503,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="E125" s="1" t="str">
-        <x:v>source_assets/art/production/ui_redesign_20261007/book_frame.png</x:v>
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_99.png</x:v>
       </x:c>
       <x:c r="F125" s="1" t="str">
-        <x:v>f11f5354f97c4ad70975f2737c69bf1691e5d848b1a3295e347facdecb9d041f</x:v>
+        <x:v>2a0e080c7d73f870c967dc1879a6f9c01ae9ac58fb4d9292d0e6fc72776527a0</x:v>
       </x:c>
       <x:c r="G125" s="1" t="str"/>
       <x:c r="H125" s="1" t="n">
@@ -5757,10 +5525,556 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="M125" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N125" s="1" t="n">
         <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>skin_122</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D126" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_122.png</x:v>
+      </x:c>
+      <x:c r="F126" t="str">
+        <x:v>fb3d51a27b91a2357c2b64a13997b93c2dfb13d5736d4300f2b0629053efd7db</x:v>
+      </x:c>
+      <x:c r="G126" t="str"/>
+      <x:c r="H126" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I126" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="K126" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="L126" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N126" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>skin_123</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D127" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_123.png</x:v>
+      </x:c>
+      <x:c r="F127" t="str">
+        <x:v>788c2bff7cbd2b1b8f6260d8f2ba95f1d1c5413f7d1d1b21cb5e6278f9320c65</x:v>
+      </x:c>
+      <x:c r="G127" t="str"/>
+      <x:c r="H127" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I127" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J127" t="n">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="K127" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="L127" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M127" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N127" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>skin_124</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D128" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_124.png</x:v>
+      </x:c>
+      <x:c r="F128" t="str">
+        <x:v>1b5c9ad9c2e860a1d0ac9af9aacde1c0729c4f66d44b82f831a2a147cde2bada</x:v>
+      </x:c>
+      <x:c r="G128" t="str"/>
+      <x:c r="H128" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I128" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J128" t="n">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="K128" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L128" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N128" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>skin_125</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D129" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_125.png</x:v>
+      </x:c>
+      <x:c r="F129" t="str">
+        <x:v>ac2efbb5ad9525914366cdc8f87b6f798ac61844760056e48b6f93d98a839927</x:v>
+      </x:c>
+      <x:c r="G129" t="str"/>
+      <x:c r="H129" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I129" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J129" t="n">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="K129" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L129" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N129" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>skin_126</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D130" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_126.png</x:v>
+      </x:c>
+      <x:c r="F130" t="str">
+        <x:v>ee765be5b1be91812318ef8c08768101eb64e02b732f9310f3a855df7899261f</x:v>
+      </x:c>
+      <x:c r="G130" t="str"/>
+      <x:c r="H130" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I130" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J130" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K130" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L130" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M130" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N130" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>skin_127</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D131" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_127.png</x:v>
+      </x:c>
+      <x:c r="F131" t="str">
+        <x:v>f79b64865e7bf7843b86a1a4833b1d03e2c1ad20b2dea199be88bda75715a3c2</x:v>
+      </x:c>
+      <x:c r="G131" t="str"/>
+      <x:c r="H131" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I131" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J131" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K131" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L131" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N131" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>skin_128</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D132" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_128.png</x:v>
+      </x:c>
+      <x:c r="F132" t="str">
+        <x:v>fea4473fb36753aced81defaeea5195fd1a08c153af586b4bd1d41f90922c848</x:v>
+      </x:c>
+      <x:c r="G132" t="str"/>
+      <x:c r="H132" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I132" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J132" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="K132" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="L132" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N132" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>skin_129</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D133" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_129.png</x:v>
+      </x:c>
+      <x:c r="F133" t="str">
+        <x:v>2becbc803ddfe5db0b8318b715354247aad16afbef2b4175ea94a15a51609553</x:v>
+      </x:c>
+      <x:c r="G133" t="str"/>
+      <x:c r="H133" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I133" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J133" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="K133" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="L133" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M133" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N133" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>skin_130</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D134" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_130.png</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>9bb502c9746d2db28ab7c78b26581cfc697617cbfe7413897e8b65f90cbc43a8</x:v>
+      </x:c>
+      <x:c r="G134" t="str"/>
+      <x:c r="H134" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I134" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J134" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K134" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L134" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N134" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>skin_131</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D135" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_131.png</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>2cbca2f3473d178897670bdd270c00babba3af9d1a37fecabe2293877eef7dfc</x:v>
+      </x:c>
+      <x:c r="G135" t="str"/>
+      <x:c r="H135" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I135" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J135" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K135" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L135" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N135" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>skin_132</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D136" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/skin_121.png</x:v>
+      </x:c>
+      <x:c r="F136" t="str">
+        <x:v>ddada5042045d532ac6eac9adff15b452157dde5ada9232da2131327028887c0</x:v>
+      </x:c>
+      <x:c r="G136" t="str"/>
+      <x:c r="H136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J136" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="K136" t="n">
+        <x:v>1254</x:v>
+      </x:c>
+      <x:c r="L136" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>skin_133</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D137" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/mint_pill_original.png</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>f5e888d0fea4da080e8f33337f5cb39ab2e51e34190bc0045502d0311f18d43d</x:v>
+      </x:c>
+      <x:c r="G137" t="str"/>
+      <x:c r="H137" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I137" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="J137" t="n">
+        <x:v>1720</x:v>
+      </x:c>
+      <x:c r="K137" t="n">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="L137" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N137" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>skin_134</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D138" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>source_assets/art/production/ui_individual_20261007/counter_green_original.png</x:v>
+      </x:c>
+      <x:c r="F138" t="str">
+        <x:v>8672aefd56bf282f72b7c83f469f9476eab6b5424f2669734a109b1e7a391f2b</x:v>
+      </x:c>
+      <x:c r="G138" t="str"/>
+      <x:c r="H138" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="I138" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J138" t="n">
+        <x:v>1664</x:v>
+      </x:c>
+      <x:c r="K138" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="L138" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N138" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ArtCut.xlsx
+++ b/design/tables/ArtCut.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtCut" sheetId="1" r:id="R004f6ab94c994b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtCut" sheetId="1" r:id="R7471734d29884bc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3361,23 +3361,23 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E74" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_36.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/sprout_heavy.png</x:v>
       </x:c>
       <x:c r="F74" s="1" t="str">
-        <x:v>a60b6d747b847c55f21c55caa2878abf6a736c7019da21a01ce8fd0a7975ff9f</x:v>
+        <x:v>5bf3b946690ebfda35b51bf9b0ebaeda43a1952cf69af78f059aa2d7c46324da</x:v>
       </x:c>
       <x:c r="G74" s="1" t="str"/>
       <x:c r="H74" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J74" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="K74" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="L74" s="1" t="n">
         <x:v>128</x:v>
@@ -3403,23 +3403,23 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E75" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_38.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/frost_deep.png</x:v>
       </x:c>
       <x:c r="F75" s="1" t="str">
-        <x:v>f2f97da73dcbb0181537d950d966bbe3103b08ef9411ac070c372c0713abfea3</x:v>
+        <x:v>b06ac04bdb0d2e2e4072f225021fab8b6f01ee008877997404e70b48d58edf6d</x:v>
       </x:c>
       <x:c r="G75" s="1" t="str"/>
       <x:c r="H75" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J75" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="K75" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="L75" s="1" t="n">
         <x:v>128</x:v>
@@ -3445,23 +3445,23 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_40.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/bloom_focus.png</x:v>
       </x:c>
       <x:c r="F76" s="1" t="str">
-        <x:v>e9efb43e4c95512de5cf8faa0979b8bf1a33f6f16a1b7167c5f5c9b3b7245311</x:v>
+        <x:v>2a59f105c3d921530f9a57a73f4a542adf19c9566bb72740e25114bedd2088d4</x:v>
       </x:c>
       <x:c r="G76" s="1" t="str"/>
       <x:c r="H76" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I76" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J76" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="K76" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="L76" s="1" t="n">
         <x:v>128</x:v>
@@ -3487,23 +3487,23 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E77" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_42.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/scope_precision.png</x:v>
       </x:c>
       <x:c r="F77" s="1" t="str">
-        <x:v>7fd95c843710d2467ee542cc56c6f3796f55f4376bf1f5a0911171dd01218841</x:v>
+        <x:v>b6f04724fed5c15ae94dfbd59ce7def72da4554c44bae41f403591f41e1a5b57</x:v>
       </x:c>
       <x:c r="G77" s="1" t="str"/>
       <x:c r="H77" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J77" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="K77" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="L77" s="1" t="n">
         <x:v>128</x:v>
@@ -3529,23 +3529,23 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E78" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_44.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/spark_focus.png</x:v>
       </x:c>
       <x:c r="F78" s="1" t="str">
-        <x:v>8e48087e0ab87901adcb22c33b23b22db189db47d082ee8f29c3483e771e39f0</x:v>
+        <x:v>f3af979b9603478f18231126ddd933d317b19f988c453415da813680bd7198bf</x:v>
       </x:c>
       <x:c r="G78" s="1" t="str"/>
       <x:c r="H78" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I78" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J78" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="K78" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="L78" s="1" t="n">
         <x:v>128</x:v>
@@ -3571,23 +3571,23 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_46.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/ember_scorch.png</x:v>
       </x:c>
       <x:c r="F79" s="1" t="str">
-        <x:v>693ed3ca5eaf0dfb073d29785d5bdcaeaa168c72cbe231703f09b67bd131df87</x:v>
+        <x:v>20853d940adc84315b30c108877053bd9f722f69b567a834000a9eb3206d2712</x:v>
       </x:c>
       <x:c r="G79" s="1" t="str"/>
       <x:c r="H79" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I79" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J79" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="K79" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="L79" s="1" t="n">
         <x:v>128</x:v>
@@ -3613,23 +3613,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E80" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_48.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/mint_focus.png</x:v>
       </x:c>
       <x:c r="F80" s="1" t="str">
-        <x:v>82127138ee12a342ab5af1269f1fea8ceb1cdddf045f929cbd00066b77bb4fab</x:v>
+        <x:v>264a07975ea436b86541cf48c66293f8cb122e04cac50c2be3c78eb24e18ce7e</x:v>
       </x:c>
       <x:c r="G80" s="1" t="str"/>
       <x:c r="H80" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I80" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J80" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="K80" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="L80" s="1" t="n">
         <x:v>128</x:v>
@@ -3655,23 +3655,23 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E81" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_50.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/fan_spread.png</x:v>
       </x:c>
       <x:c r="F81" s="1" t="str">
-        <x:v>d946250b58c516f95e0ae8b9760fcc6fdf1f6eaddc2f46714df40430197c70eb</x:v>
+        <x:v>b620bc845826222de1e8045b8188d07b3165ffd1bf929b2c4b245a3b85014679</x:v>
       </x:c>
       <x:c r="G81" s="1" t="str"/>
       <x:c r="H81" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I81" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J81" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="K81" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="L81" s="1" t="n">
         <x:v>128</x:v>
@@ -3697,23 +3697,23 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E82" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_37.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/sprout_burst.png</x:v>
       </x:c>
       <x:c r="F82" s="1" t="str">
-        <x:v>71fd7ac29c78649c3ec20e9c67a400e1a6db27da27ba4a5ee80ec001094bce5d</x:v>
+        <x:v>bfdbf7668c7817481e9122e7ce51694ee26ab2b4311b3f899e4ff9d6fadfbb69</x:v>
       </x:c>
       <x:c r="G82" s="1" t="str"/>
       <x:c r="H82" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I82" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J82" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="K82" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="L82" s="1" t="n">
         <x:v>128</x:v>
@@ -3739,23 +3739,23 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_39.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/frost_dual.png</x:v>
       </x:c>
       <x:c r="F83" s="1" t="str">
-        <x:v>816446b7f622cac60a26748c7ad3502fa76fbb39686b60c5a10344bd7c4258ae</x:v>
+        <x:v>68de27d45eb8ac0405c50729cda0e90372cd046fbe8ae6866cc659cbbfee8f8f</x:v>
       </x:c>
       <x:c r="G83" s="1" t="str"/>
       <x:c r="H83" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I83" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J83" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="K83" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="L83" s="1" t="n">
         <x:v>128</x:v>
@@ -3781,23 +3781,23 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E84" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_41.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/bloom_wide.png</x:v>
       </x:c>
       <x:c r="F84" s="1" t="str">
-        <x:v>efb8f37399281bc9fe07971384ca6ab0bf40f199917f137b07e2a830af75614c</x:v>
+        <x:v>8517eebbeed5d4c24b4156ed11f74a40c74131fc3c8a71fbdac567458725093e</x:v>
       </x:c>
       <x:c r="G84" s="1" t="str"/>
       <x:c r="H84" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I84" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J84" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="K84" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="L84" s="1" t="n">
         <x:v>128</x:v>
@@ -3823,23 +3823,23 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E85" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_43.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/scope_pierce.png</x:v>
       </x:c>
       <x:c r="F85" s="1" t="str">
-        <x:v>9cde2abd17b546fff7a02fb94bb804423f8e143373ecb83d3b2d3ca062ae9eb4</x:v>
+        <x:v>0e8741d81b7d729fd731f0f44306a5754f9628987d025337fa82db79ac345235</x:v>
       </x:c>
       <x:c r="G85" s="1" t="str"/>
       <x:c r="H85" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J85" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="K85" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="L85" s="1" t="n">
         <x:v>128</x:v>
@@ -3865,23 +3865,23 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E86" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_45.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/spark_chain.png</x:v>
       </x:c>
       <x:c r="F86" s="1" t="str">
-        <x:v>ad5096d1ce3b8da27ec1c003bf90d0016d5b67eb464b38b55cbc74a37063a511</x:v>
+        <x:v>0040cf4791335691173ac5686788c249ad33e238584dc1c7bc5ede1277fedfe7</x:v>
       </x:c>
       <x:c r="G86" s="1" t="str"/>
       <x:c r="H86" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J86" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="K86" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="L86" s="1" t="n">
         <x:v>128</x:v>
@@ -3907,23 +3907,23 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E87" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_47.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/ember_burst.png</x:v>
       </x:c>
       <x:c r="F87" s="1" t="str">
-        <x:v>355c70631488cb95ae429ed1292ecd9aa4d5ec0020edc91c26a7627d39d574f4</x:v>
+        <x:v>9d887bfdd668401f0ac38059ded881ee9f34cf159a22b7150fb0b79bab056f40</x:v>
       </x:c>
       <x:c r="G87" s="1" t="str"/>
       <x:c r="H87" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J87" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="K87" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="L87" s="1" t="n">
         <x:v>128</x:v>
@@ -3949,23 +3949,23 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E88" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_49.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/mint_dual.png</x:v>
       </x:c>
       <x:c r="F88" s="1" t="str">
-        <x:v>4fb88a4fcdb87bca287803aee933c00a46a5a69d28683da0d3a14cbe515ff896</x:v>
+        <x:v>46cc8720ff6af29e1ba6d062573585aa607aeb7d4841cf2f9881d3445acdf84f</x:v>
       </x:c>
       <x:c r="G88" s="1" t="str"/>
       <x:c r="H88" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I88" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J88" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="K88" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="L88" s="1" t="n">
         <x:v>128</x:v>
@@ -3991,23 +3991,23 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E89" s="1" t="str">
-        <x:v>source_assets/art/production/ui_individual_20261007/frame_51.png</x:v>
+        <x:v>source_assets/art/production/staff_progression_20261008/fan_volley.png</x:v>
       </x:c>
       <x:c r="F89" s="1" t="str">
-        <x:v>d2a00aeecade7b3bf174b4a0b8dba42f5e04e277fb08d57c2add8d760973d5df</x:v>
+        <x:v>173f24382b6f3d6a36e22d742377c94b5f23c1115e944b4ef5489723fa5f030d</x:v>
       </x:c>
       <x:c r="G89" s="1" t="str"/>
       <x:c r="H89" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I89" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J89" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="K89" s="1" t="n">
-        <x:v>240</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="L89" s="1" t="n">
         <x:v>128</x:v>
@@ -6074,6 +6074,384 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N138" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>frame_84</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D139" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/sprout_level2.png</x:v>
+      </x:c>
+      <x:c r="F139" t="str">
+        <x:v>795cf0f37e677387f7096b12c8af890336e1745e7d12cc0a90f5d2502cbb37fa</x:v>
+      </x:c>
+      <x:c r="G139" t="str"/>
+      <x:c r="H139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I139" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J139" t="n">
+        <x:v>1234</x:v>
+      </x:c>
+      <x:c r="K139" t="n">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="L139" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N139" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>frame_85</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D140" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/frost_level2.png</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>95177938a4d82391597f3a4750ae29a5346ab1405f6e293f75d69e160bb5e8c3</x:v>
+      </x:c>
+      <x:c r="G140" t="str"/>
+      <x:c r="H140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I140" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J140" t="n">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="K140" t="n">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="L140" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N140" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>frame_86</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D141" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/bloom_level2.png</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>52fbb1429ce9590a540902a0a45ce35776cf4b927ac168b88bf06776e2884ca7</x:v>
+      </x:c>
+      <x:c r="G141" t="str"/>
+      <x:c r="H141" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I141" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J141" t="n">
+        <x:v>1166</x:v>
+      </x:c>
+      <x:c r="K141" t="n">
+        <x:v>1181</x:v>
+      </x:c>
+      <x:c r="L141" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N141" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>frame_87</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D142" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/scope_level2.png</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>0423c054e275edd8d2818bcbf45ac8cf76d9c9952bfb7ea1fca43faa4b714d85</x:v>
+      </x:c>
+      <x:c r="G142" t="str"/>
+      <x:c r="H142" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I142" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J142" t="n">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="K142" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="L142" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N142" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>frame_88</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D143" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/spark_level2.png</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>7189e0741f33d09c8cb9fbd3512e9e6505323c1d351fe68f35e86289b94f54f3</x:v>
+      </x:c>
+      <x:c r="G143" t="str"/>
+      <x:c r="H143" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I143" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J143" t="n">
+        <x:v>1191</x:v>
+      </x:c>
+      <x:c r="K143" t="n">
+        <x:v>1161</x:v>
+      </x:c>
+      <x:c r="L143" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N143" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>frame_89</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D144" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/ember_level2.png</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>47a149376cd15ed4a02b065f9483843c49a32cf3c5a7bff4bd929749ebcf80e0</x:v>
+      </x:c>
+      <x:c r="G144" t="str"/>
+      <x:c r="H144" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I144" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J144" t="n">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c r="K144" t="n">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c r="L144" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N144" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>frame_90</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D145" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/mint_level2.png</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>7222c0aeaeb3decb0e2eb89521953a0337fe625048e841de0716240a305ee041</x:v>
+      </x:c>
+      <x:c r="G145" t="str"/>
+      <x:c r="H145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I145" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J145" t="n">
+        <x:v>1193</x:v>
+      </x:c>
+      <x:c r="K145" t="n">
+        <x:v>1171</x:v>
+      </x:c>
+      <x:c r="L145" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N145" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>frame_91</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>frame</x:v>
+      </x:c>
+      <x:c r="D146" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/fan_level2.png</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>4051a168e761cac9472ad64dd94c3112d43422da73d5d234ae3c4fa2ae4eb7e2</x:v>
+      </x:c>
+      <x:c r="G146" t="str"/>
+      <x:c r="H146" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I146" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J146" t="n">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="K146" t="n">
+        <x:v>1192</x:v>
+      </x:c>
+      <x:c r="L146" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N146" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>skin_135</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>skin</x:v>
+      </x:c>
+      <x:c r="D147" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>source_assets/art/production/staff_progression_20261008/rank_star.png</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>0dfd3ea5cc0c3be729cd86a9012c8785d9463bae4bbdb6fd1b172c26d2031c09</x:v>
+      </x:c>
+      <x:c r="G147" t="str"/>
+      <x:c r="H147" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I147" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="J147" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="K147" t="n">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="L147" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N147" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
